--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$193</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7250" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7213" uniqueCount="816">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T07:40:29+00:00</t>
+    <t>2026-08-24T13:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,13 +120,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() xor value.exists().not() implies dataAbsentReason.exists()}mii-lab-3:Every coding of a coded laboratory result contains both system and code. {value.ofType(CodeableConcept).coding.all(system.exists() and code.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -633,7 +633,7 @@
     <t>interpretationsbeeinflussendeEigenschaft</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/InterpretationsbeeinflussendeEigenschaft|2027.0.0}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/InterpretationsbeeinflussendeEigenschaft}
 </t>
   </si>
   <si>
@@ -763,7 +763,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-identifier-type-codes|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-identifier-type-codes</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1080,7 +1080,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1301,55 +1301,93 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc</t>
+  </si>
+  <si>
+    <t>loinc</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Intensional Value Set Definition: LOINC {  {    STATUS in {ACTIVE}    CLASSTYPE in {1}    CLASS exclude {CHALSKIN, H&amp;P.HX.LAB, H&amp;P.HX, NR STATS, PATH.PROTOCOLS.*}  } }</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-pathology-observations-uv-ips|2.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-pathology-observations-uv-ips</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1583,7 +1621,7 @@
     <t>QuelleKlinischesBezugsdatum</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum|2027.0.0}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum}
 </t>
   </si>
   <si>
@@ -1721,7 +1759,7 @@
     <t>pqTranslation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {extension-quantity-translation|5.3.0}
+    <t xml:space="preserve">Extension {extension-quantity-translation}
 </t>
   </si>
   <si>
@@ -1781,7 +1819,7 @@
     <t>quantityPrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {quantity-precision|5.3.0}
+    <t xml:space="preserve">Extension {quantity-precision}
 </t>
   </si>
   <si>
@@ -1909,6 +1947,9 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-codiert</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
@@ -1921,85 +1962,46 @@
     <t>Observation.value[x].coding</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ</t>
-  </si>
-  <si>
-    <t>qualitativ</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-qualitativ|2027.0.0</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.id</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
   </si>
   <si>
     <t>Observation.value[x].coding.id</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.extension</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
   </si>
   <si>
     <t>Observation.value[x].coding.extension</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.system</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
   </si>
   <si>
     <t>Observation.value[x].coding.system</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.version</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
   </si>
   <si>
     <t>Observation.value[x].coding.version</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.code</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
   </si>
   <si>
     <t>Observation.value[x].coding.code</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.display</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
   </si>
   <si>
     <t>Observation.value[x].coding.display</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.userSelected</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ</t>
-  </si>
-  <si>
-    <t>semiquantitativ</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-semiquantitativ|2027.0.0</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.userSelected</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
@@ -2509,12 +2511,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2773,100 +2769,102 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2884,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO194"/>
+  <dimension ref="A1:AO193"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -2912,7 +2910,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="140.3671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="93.92578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="86.3984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3056,10 +3054,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -3141,7 +3139,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>
@@ -11442,7 +11440,7 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Y73" t="s" s="2">
         <v>412</v>
@@ -11728,7 +11726,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>421</v>
       </c>
@@ -11805,16 +11803,14 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>252</v>
@@ -12198,7 +12194,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>425</v>
       </c>
@@ -12217,7 +12213,7 @@
         <v>92</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
@@ -12668,14 +12664,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>429</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12684,10 +12682,10 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12696,19 +12694,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12718,7 +12716,7 @@
         <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>82</v>
@@ -12733,13 +12731,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12757,13 +12755,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12778,7 +12776,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>307</v>
+        <v>253</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12787,12 +12785,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12800,35 +12798,31 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>431</v>
+        <v>106</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>432</v>
+        <v>107</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12876,7 +12870,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>430</v>
+        <v>109</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12888,19 +12882,19 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12908,21 +12902,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12934,15 +12928,17 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12979,31 +12975,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -13021,46 +13017,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13096,31 +13094,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13129,7 +13127,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -13140,10 +13138,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13169,13 +13167,13 @@
         <v>106</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>442</v>
+        <v>271</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>443</v>
+        <v>272</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>444</v>
+        <v>273</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13225,7 +13223,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>445</v>
+        <v>274</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13234,7 +13232,7 @@
         <v>92</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>104</v>
@@ -13246,7 +13244,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -13255,12 +13253,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13268,13 +13266,13 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>82</v>
@@ -13283,18 +13281,18 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>448</v>
+        <v>278</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13318,13 +13316,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13342,7 +13340,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>453</v>
+        <v>282</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13363,7 +13361,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -13374,10 +13372,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13400,18 +13398,18 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>455</v>
+        <v>286</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13459,7 +13457,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>458</v>
+        <v>289</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13480,7 +13478,7 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
@@ -13491,10 +13489,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13517,18 +13515,20 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>460</v>
+        <v>294</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>461</v>
+        <v>295</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13576,7 +13576,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>463</v>
+        <v>298</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13597,7 +13597,7 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
@@ -13608,10 +13608,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13622,7 +13622,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13634,18 +13634,20 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>465</v>
+        <v>106</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>466</v>
+        <v>302</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>467</v>
+        <v>303</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13693,13 +13695,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>464</v>
+        <v>306</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13714,10 +13716,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>416</v>
+        <v>307</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13725,18 +13727,18 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>92</v>
@@ -13751,19 +13753,19 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>472</v>
+        <v>444</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>474</v>
+        <v>446</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13812,7 +13814,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13827,16 +13829,16 @@
         <v>104</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13844,10 +13846,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13959,10 +13961,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14076,10 +14078,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14105,13 +14107,13 @@
         <v>106</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14161,7 +14163,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14170,7 +14172,7 @@
         <v>92</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>104</v>
@@ -14193,10 +14195,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14222,13 +14224,13 @@
         <v>133</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14257,10 +14259,10 @@
         <v>149</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14278,7 +14280,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14310,10 +14312,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14339,13 +14341,13 @@
         <v>203</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14395,7 +14397,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14427,10 +14429,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14456,13 +14458,13 @@
         <v>106</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14512,7 +14514,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14542,26 +14544,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -14570,20 +14572,18 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14631,46 +14631,46 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>492</v>
+        <v>104</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>495</v>
+        <v>450</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14680,25 +14680,29 @@
         <v>92</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>106</v>
+        <v>483</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14746,7 +14750,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>109</v>
+        <v>481</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14758,19 +14762,19 @@
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14778,10 +14782,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14792,7 +14796,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14804,13 +14808,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14849,29 +14853,31 @@
         <v>82</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC102" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14889,28 +14895,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
@@ -14919,15 +14923,17 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>502</v>
+        <v>112</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>503</v>
+        <v>113</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14964,16 +14970,16 @@
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>119</v>
@@ -14985,7 +14991,7 @@
         <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>120</v>
@@ -15006,12 +15012,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15025,24 +15031,26 @@
         <v>92</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>487</v>
+        <v>106</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15091,7 +15099,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15100,10 +15108,10 @@
         <v>92</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -15121,12 +15129,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15140,7 +15148,7 @@
         <v>92</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>82</v>
@@ -15149,16 +15157,16 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>510</v>
+        <v>460</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>511</v>
+        <v>461</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>512</v>
+        <v>462</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15184,13 +15192,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15208,7 +15216,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15229,21 +15237,21 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15254,10 +15262,10 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>82</v>
@@ -15266,18 +15274,18 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>516</v>
+        <v>203</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15325,13 +15333,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>515</v>
+        <v>470</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15340,16 +15348,16 @@
         <v>104</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15357,10 +15365,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15374,7 +15382,7 @@
         <v>92</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
@@ -15383,20 +15391,18 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>526</v>
+        <v>473</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15432,17 +15438,19 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AC107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>523</v>
+        <v>475</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15451,7 +15459,7 @@
         <v>92</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>104</v>
@@ -15460,34 +15468,32 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>92</v>
@@ -15502,19 +15508,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>537</v>
+        <v>499</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15563,7 +15569,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15572,33 +15578,33 @@
         <v>92</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>104</v>
+        <v>504</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15624,10 +15630,10 @@
         <v>106</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>107</v>
+        <v>509</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>108</v>
+        <v>510</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15710,14 +15716,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15739,14 +15745,12 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15785,9 +15789,7 @@
       <c r="AB110" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC110" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15825,15 +15827,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>82</v>
@@ -15843,10 +15845,10 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
@@ -15855,17 +15857,15 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15923,7 +15923,7 @@
         <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>120</v>
@@ -15944,12 +15944,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15957,35 +15957,31 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>553</v>
+        <v>518</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -16033,7 +16029,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16045,7 +16041,7 @@
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16054,7 +16050,7 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
@@ -16063,12 +16059,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>559</v>
+        <v>521</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16082,24 +16078,26 @@
         <v>92</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16148,7 +16146,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>109</v>
+        <v>521</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16160,7 +16158,7 @@
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16169,10 +16167,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16180,10 +16178,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>561</v>
+        <v>527</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>562</v>
+        <v>527</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16203,19 +16201,21 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>112</v>
+        <v>528</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>193</v>
+        <v>529</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>194</v>
+        <v>530</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -16251,17 +16251,19 @@
         <v>82</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC114" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>119</v>
+        <v>527</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16273,34 +16275,32 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16318,21 +16318,23 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>565</v>
+        <v>536</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>566</v>
+        <v>537</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16368,56 +16370,56 @@
         <v>82</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>201</v>
+        <v>543</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>229</v>
+        <v>545</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C116" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="D116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16429,25 +16431,29 @@
         <v>92</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16495,7 +16501,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16504,33 +16510,33 @@
         <v>92</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16544,33 +16550,29 @@
         <v>92</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>575</v>
+        <v>107</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>576</v>
+        <v>108</v>
       </c>
       <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>577</v>
-      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q117" t="s" s="2">
-        <v>578</v>
-      </c>
+      <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16590,13 +16592,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16614,7 +16616,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>581</v>
+        <v>109</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16626,7 +16628,7 @@
         <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>82</v>
@@ -16635,7 +16637,7 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
@@ -16644,46 +16646,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>584</v>
+        <v>555</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>585</v>
+        <v>113</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16719,31 +16721,31 @@
         <v>82</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>588</v>
+        <v>119</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
@@ -16752,7 +16754,7 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -16761,52 +16763,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>133</v>
+        <v>558</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>82</v>
@@ -16848,19 +16852,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>596</v>
+        <v>119</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -16869,7 +16873,7 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>82</v>
@@ -16880,10 +16884,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>598</v>
+        <v>562</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16906,19 +16910,19 @@
         <v>93</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>600</v>
+        <v>565</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>601</v>
+        <v>566</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>602</v>
+        <v>567</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>603</v>
+        <v>568</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16967,7 +16971,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>604</v>
+        <v>569</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16988,7 +16992,7 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>82</v>
@@ -16997,16 +17001,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>605</v>
+        <v>571</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17018,29 +17020,25 @@
         <v>92</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17088,7 +17086,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>523</v>
+        <v>109</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17097,33 +17095,33 @@
         <v>92</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>541</v>
+        <v>574</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17134,7 +17132,7 @@
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17146,13 +17144,13 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17191,31 +17189,29 @@
         <v>82</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17233,26 +17229,28 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="D123" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>82</v>
@@ -17261,16 +17259,16 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>112</v>
+        <v>577</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>113</v>
+        <v>578</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>114</v>
+        <v>579</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>115</v>
+        <v>580</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17308,16 +17306,16 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
         <v>119</v>
@@ -17329,7 +17327,7 @@
         <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>120</v>
@@ -17341,7 +17339,7 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>82</v>
@@ -17352,10 +17350,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17363,35 +17361,31 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>145</v>
+        <v>564</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>247</v>
+        <v>583</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17427,29 +17421,31 @@
         <v>82</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AC124" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>252</v>
+        <v>584</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
@@ -17458,7 +17454,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17469,14 +17465,12 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>611</v>
+        <v>585</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17491,30 +17485,30 @@
         <v>93</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>247</v>
+        <v>587</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>250</v>
+        <v>589</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q125" s="2"/>
+      <c r="Q125" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="R125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17536,9 +17530,11 @@
       <c r="X125" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Y125" s="2"/>
+      <c r="Y125" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
@@ -17556,13 +17552,13 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>252</v>
+        <v>593</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>82</v>
@@ -17577,7 +17573,7 @@
         <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>253</v>
+        <v>594</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17586,12 +17582,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17599,31 +17595,33 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>107</v>
+        <v>597</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>108</v>
+        <v>598</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17671,7 +17669,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>109</v>
+        <v>600</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17683,7 +17681,7 @@
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>82</v>
@@ -17692,7 +17690,7 @@
         <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17701,52 +17699,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>113</v>
+        <v>604</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>82</v>
@@ -17776,31 +17774,31 @@
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>119</v>
+        <v>608</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>82</v>
@@ -17809,7 +17807,7 @@
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17820,10 +17818,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17831,7 +17829,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>92</v>
@@ -17846,19 +17844,19 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>262</v>
+        <v>612</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>263</v>
+        <v>613</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>264</v>
+        <v>614</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>265</v>
+        <v>615</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17907,7 +17905,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>267</v>
+        <v>616</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17928,7 +17926,7 @@
         <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>268</v>
+        <v>601</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -17937,14 +17935,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="D129" t="s" s="2">
         <v>82</v>
       </c>
@@ -17956,7 +17956,7 @@
         <v>92</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>82</v>
@@ -17965,18 +17965,20 @@
         <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>271</v>
+        <v>550</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>272</v>
+        <v>551</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O129" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18000,13 +18002,11 @@
         <v>82</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>82</v>
@@ -18024,7 +18024,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>274</v>
+        <v>535</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18033,7 +18033,7 @@
         <v>92</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>104</v>
@@ -18042,24 +18042,24 @@
         <v>82</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>275</v>
+        <v>545</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>623</v>
+        <v>553</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18073,27 +18073,25 @@
         <v>92</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>280</v>
-      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18141,7 +18139,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18153,7 +18151,7 @@
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18162,7 +18160,7 @@
         <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
@@ -18173,21 +18171,21 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>82</v>
@@ -18196,21 +18194,21 @@
         <v>82</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>286</v>
+        <v>113</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18246,31 +18244,31 @@
         <v>82</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>289</v>
+        <v>119</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>82</v>
@@ -18279,7 +18277,7 @@
         <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
@@ -18288,12 +18286,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18301,13 +18299,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>82</v>
@@ -18316,19 +18314,19 @@
         <v>93</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18377,13 +18375,13 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
@@ -18398,7 +18396,7 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18407,16 +18405,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C133" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18428,29 +18424,25 @@
         <v>92</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18474,11 +18466,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="Y133" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z133" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18496,19 +18490,19 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
@@ -18517,7 +18511,7 @@
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
@@ -18528,21 +18522,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18554,15 +18548,17 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18599,31 +18595,31 @@
         <v>82</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>82</v>
@@ -18641,46 +18637,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -18716,31 +18714,31 @@
         <v>82</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
@@ -18749,7 +18747,7 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
@@ -18760,10 +18758,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18786,20 +18784,18 @@
         <v>93</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18847,7 +18843,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18868,7 +18864,7 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18877,12 +18873,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18890,13 +18886,13 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>82</v>
@@ -18905,18 +18901,18 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -18964,7 +18960,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18985,7 +18981,7 @@
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -18994,12 +18990,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19013,7 +19009,7 @@
         <v>92</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>82</v>
@@ -19022,17 +19018,17 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19081,7 +19077,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19102,7 +19098,7 @@
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
@@ -19116,7 +19112,7 @@
         <v>636</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19139,17 +19135,19 @@
         <v>93</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O139" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -19198,7 +19196,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19219,7 +19217,7 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
@@ -19230,10 +19228,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19256,19 +19254,19 @@
         <v>93</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19317,7 +19315,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19338,7 +19336,7 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -19347,14 +19345,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C141" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="D141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19366,7 +19366,7 @@
         <v>92</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>82</v>
@@ -19375,19 +19375,19 @@
         <v>93</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>106</v>
+        <v>642</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>302</v>
+        <v>550</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>303</v>
+        <v>551</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>304</v>
+        <v>539</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>305</v>
+        <v>540</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19436,7 +19436,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>306</v>
+        <v>535</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19445,7 +19445,7 @@
         <v>92</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>104</v>
@@ -19454,27 +19454,27 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>307</v>
+        <v>545</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
@@ -19496,19 +19496,19 @@
         <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="M142" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N142" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="O142" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19557,7 +19557,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19566,7 +19566,7 @@
         <v>92</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>104</v>
@@ -19575,28 +19575,26 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19614,22 +19612,22 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>645</v>
+        <v>232</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>538</v>
+        <v>647</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>539</v>
+        <v>648</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>527</v>
+        <v>649</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>528</v>
+        <v>650</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19654,13 +19652,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19678,7 +19676,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>523</v>
+        <v>646</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19687,7 +19685,7 @@
         <v>92</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>531</v>
+        <v>653</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>104</v>
@@ -19696,35 +19694,35 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>533</v>
+        <v>229</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>93</v>
@@ -19739,16 +19737,16 @@
         <v>232</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -19776,10 +19774,10 @@
         <v>149</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19797,16 +19795,16 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>104</v>
@@ -19815,28 +19813,28 @@
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>229</v>
+        <v>663</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>82</v>
+        <v>664</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19855,19 +19853,19 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>232</v>
+        <v>666</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -19892,13 +19890,13 @@
         <v>82</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -19916,7 +19914,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -19934,24 +19932,24 @@
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>664</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19962,10 +19960,10 @@
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>82</v>
@@ -19974,20 +19972,18 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>666</v>
+        <v>232</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>670</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>82</v>
       </c>
@@ -20011,13 +20007,13 @@
         <v>82</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>82</v>
+        <v>677</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20035,13 +20031,13 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>82</v>
@@ -20053,24 +20049,24 @@
         <v>82</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20081,10 +20077,10 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>82</v>
@@ -20096,15 +20092,17 @@
         <v>232</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O147" s="2"/>
+        <v>684</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>685</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20131,10 +20129,10 @@
         <v>157</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -20152,7 +20150,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20170,24 +20168,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>678</v>
+        <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>680</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20201,7 +20199,7 @@
         <v>92</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>82</v>
@@ -20210,20 +20208,16 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>682</v>
+        <v>107</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>82</v>
       </c>
@@ -20247,13 +20241,13 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>686</v>
+        <v>82</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20271,7 +20265,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>681</v>
+        <v>109</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20283,7 +20277,7 @@
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>82</v>
@@ -20292,7 +20286,7 @@
         <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
@@ -20303,21 +20297,21 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>82</v>
@@ -20329,15 +20323,17 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20374,31 +20370,31 @@
         <v>82</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>82</v>
@@ -20416,16 +20412,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20435,27 +20431,29 @@
         <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>113</v>
+        <v>247</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>114</v>
+        <v>248</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O150" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
       </c>
@@ -20491,19 +20489,19 @@
         <v>82</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>119</v>
+        <v>252</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20515,7 +20513,7 @@
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>82</v>
@@ -20524,7 +20522,7 @@
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20533,12 +20531,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20549,32 +20547,28 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
       </c>
@@ -20622,19 +20616,19 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>82</v>
@@ -20643,7 +20637,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20654,21 +20648,21 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>82</v>
@@ -20680,15 +20674,17 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20725,31 +20721,31 @@
         <v>82</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>82</v>
@@ -20767,46 +20763,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O153" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -20842,31 +20840,31 @@
         <v>82</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>82</v>
@@ -20875,7 +20873,7 @@
         <v>82</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>82</v>
@@ -20884,12 +20882,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20897,13 +20895,13 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>82</v>
@@ -20912,20 +20910,18 @@
         <v>93</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
@@ -20973,7 +20969,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20994,7 +20990,7 @@
         <v>82</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>82</v>
@@ -21003,12 +20999,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21016,13 +21012,13 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>82</v>
@@ -21031,18 +21027,18 @@
         <v>93</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21090,7 +21086,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21111,7 +21107,7 @@
         <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
@@ -21122,10 +21118,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21133,7 +21129,7 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>92</v>
@@ -21148,17 +21144,17 @@
         <v>93</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21207,7 +21203,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21228,7 +21224,7 @@
         <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>82</v>
@@ -21237,12 +21233,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21256,7 +21252,7 @@
         <v>92</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>82</v>
@@ -21265,17 +21261,19 @@
         <v>93</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O157" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21324,7 +21322,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21345,7 +21343,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21356,10 +21354,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21382,19 +21380,19 @@
         <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -21443,7 +21441,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21464,7 +21462,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21473,12 +21471,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21492,29 +21490,27 @@
         <v>92</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>106</v>
+        <v>701</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>302</v>
+        <v>702</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>303</v>
+        <v>703</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21562,7 +21558,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>306</v>
+        <v>700</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21580,24 +21576,24 @@
         <v>82</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>82</v>
+        <v>705</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>307</v>
+        <v>706</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>82</v>
+        <v>707</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21611,7 +21607,7 @@
         <v>92</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>82</v>
@@ -21620,17 +21616,15 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>701</v>
+        <v>106</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>702</v>
+        <v>107</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -21679,7 +21673,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>700</v>
+        <v>109</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21691,41 +21685,41 @@
         <v>82</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>705</v>
+        <v>82</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>706</v>
+        <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>707</v>
+        <v>82</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>82</v>
@@ -21737,15 +21731,17 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N161" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21782,31 +21778,31 @@
         <v>82</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>82</v>
@@ -21824,44 +21820,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>115</v>
+        <v>456</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21899,31 +21895,31 @@
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>119</v>
+        <v>457</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>82</v>
@@ -21941,12 +21937,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21960,7 +21956,7 @@
         <v>92</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>82</v>
@@ -21969,16 +21965,16 @@
         <v>93</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22004,13 +22000,13 @@
         <v>82</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22028,7 +22024,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22037,7 +22033,7 @@
         <v>92</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>104</v>
@@ -22058,12 +22054,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22077,7 +22073,7 @@
         <v>92</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>82</v>
@@ -22086,16 +22082,16 @@
         <v>93</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22121,13 +22117,13 @@
         <v>82</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22145,7 +22141,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22175,12 +22171,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22194,7 +22190,7 @@
         <v>92</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>82</v>
@@ -22203,16 +22199,16 @@
         <v>93</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22262,7 +22258,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22292,12 +22288,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22311,25 +22307,25 @@
         <v>92</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>106</v>
+        <v>715</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>460</v>
+        <v>716</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>461</v>
+        <v>717</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>462</v>
+        <v>718</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22379,7 +22375,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>463</v>
+        <v>714</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22397,24 +22393,24 @@
         <v>82</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>82</v>
+        <v>719</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>82</v>
+        <v>720</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>82</v>
+        <v>721</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22428,7 +22424,7 @@
         <v>92</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>82</v>
@@ -22437,17 +22433,15 @@
         <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>715</v>
+        <v>106</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>716</v>
+        <v>107</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22496,7 +22490,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>714</v>
+        <v>109</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22508,41 +22502,41 @@
         <v>82</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>719</v>
+        <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>720</v>
+        <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
@@ -22554,15 +22548,17 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22599,31 +22595,31 @@
         <v>82</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>82</v>
@@ -22641,44 +22637,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>115</v>
+        <v>456</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22716,31 +22712,31 @@
         <v>82</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>119</v>
+        <v>457</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>82</v>
@@ -22758,12 +22754,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22777,7 +22773,7 @@
         <v>92</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>82</v>
@@ -22786,16 +22782,16 @@
         <v>93</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -22821,13 +22817,13 @@
         <v>82</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>82</v>
@@ -22845,7 +22841,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22854,7 +22850,7 @@
         <v>92</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>104</v>
@@ -22875,12 +22871,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22894,7 +22890,7 @@
         <v>92</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>82</v>
@@ -22903,16 +22899,16 @@
         <v>93</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -22938,13 +22934,13 @@
         <v>82</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -22962,7 +22958,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22992,12 +22988,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23011,7 +23007,7 @@
         <v>92</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>82</v>
@@ -23020,16 +23016,16 @@
         <v>93</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23079,7 +23075,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23109,12 +23105,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23125,30 +23121,32 @@
         <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>106</v>
+        <v>729</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>460</v>
+        <v>730</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>461</v>
+        <v>731</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O173" s="2"/>
+        <v>732</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>733</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>82</v>
       </c>
@@ -23196,19 +23194,19 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>463</v>
+        <v>728</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>104</v>
+        <v>734</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>82</v>
@@ -23217,7 +23215,7 @@
         <v>82</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>82</v>
+        <v>735</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>82</v>
@@ -23226,12 +23224,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23242,10 +23240,10 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>82</v>
@@ -23254,20 +23252,16 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>729</v>
+        <v>106</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>730</v>
+        <v>107</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N174" s="2"/>
+      <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23315,19 +23309,19 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>728</v>
+        <v>109</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>734</v>
+        <v>82</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>82</v>
@@ -23336,7 +23330,7 @@
         <v>82</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>735</v>
+        <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>82</v>
@@ -23347,21 +23341,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>82</v>
@@ -23373,15 +23367,17 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N175" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23430,19 +23426,19 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>82</v>
@@ -23462,14 +23458,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>111</v>
+        <v>739</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -23482,24 +23478,26 @@
         <v>82</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K176" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>113</v>
+        <v>740</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>114</v>
+        <v>741</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O176" s="2"/>
+      <c r="O176" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23547,7 +23545,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>119</v>
+        <v>743</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23577,48 +23575,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>739</v>
+        <v>82</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>112</v>
+        <v>745</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>747</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23666,19 +23660,19 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>82</v>
+        <v>748</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>82</v>
@@ -23687,7 +23681,7 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>82</v>
@@ -23698,10 +23692,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23727,10 +23721,10 @@
         <v>745</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -23781,7 +23775,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23811,12 +23805,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23830,7 +23824,7 @@
         <v>92</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>82</v>
@@ -23839,16 +23833,20 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>745</v>
+        <v>232</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
+        <v>755</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>757</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
       </c>
@@ -23872,13 +23870,13 @@
         <v>82</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>82</v>
+        <v>758</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -23896,7 +23894,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23905,7 +23903,7 @@
         <v>92</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>748</v>
+        <v>82</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>104</v>
@@ -23914,10 +23912,10 @@
         <v>82</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>82</v>
+        <v>760</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -23928,10 +23926,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23942,7 +23940,7 @@
         <v>80</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>82</v>
@@ -23957,16 +23955,16 @@
         <v>232</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -23991,13 +23989,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -24015,13 +24013,13 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>82</v>
@@ -24047,10 +24045,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24061,7 +24059,7 @@
         <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>82</v>
@@ -24073,19 +24071,17 @@
         <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>232</v>
+        <v>642</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>765</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24110,13 +24106,13 @@
         <v>82</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>767</v>
+        <v>82</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>768</v>
+        <v>82</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>82</v>
@@ -24134,13 +24130,13 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>82</v>
@@ -24152,10 +24148,10 @@
         <v>82</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>760</v>
+        <v>82</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>761</v>
+        <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>82</v>
@@ -24166,10 +24162,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24192,18 +24188,16 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>642</v>
+        <v>106</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="N182" s="2"/>
-      <c r="O182" t="s" s="2">
-        <v>772</v>
-      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>82</v>
       </c>
@@ -24251,7 +24245,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24272,7 +24266,7 @@
         <v>82</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>82</v>
@@ -24283,10 +24277,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24297,7 +24291,7 @@
         <v>80</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>82</v>
@@ -24306,18 +24300,20 @@
         <v>82</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>106</v>
+        <v>777</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="N183" s="2"/>
+        <v>779</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>780</v>
+      </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24366,13 +24362,13 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>82</v>
@@ -24387,7 +24383,7 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>749</v>
+        <v>781</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>82</v>
@@ -24398,10 +24394,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24424,16 +24420,16 @@
         <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24483,7 +24479,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -24515,10 +24511,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24541,18 +24537,20 @@
         <v>93</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>783</v>
+        <v>729</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>791</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24600,7 +24598,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24621,7 +24619,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24632,10 +24630,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24646,7 +24644,7 @@
         <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>82</v>
@@ -24655,23 +24653,19 @@
         <v>82</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>729</v>
+        <v>106</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>788</v>
+        <v>107</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>791</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N186" s="2"/>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>82</v>
       </c>
@@ -24719,19 +24713,19 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>787</v>
+        <v>109</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>82</v>
@@ -24740,7 +24734,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>792</v>
+        <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24751,21 +24745,21 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>82</v>
@@ -24777,15 +24771,17 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N187" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -24834,19 +24830,19 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>82</v>
@@ -24866,14 +24862,14 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>111</v>
+        <v>739</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -24886,24 +24882,26 @@
         <v>82</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>113</v>
+        <v>740</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>114</v>
+        <v>741</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O188" s="2"/>
+      <c r="O188" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
       </c>
@@ -24951,7 +24949,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>119</v>
+        <v>743</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24983,45 +24981,45 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>739</v>
+        <v>82</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J189" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>740</v>
+        <v>797</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>741</v>
+        <v>798</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>115</v>
+        <v>799</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>742</v>
+        <v>411</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
@@ -25046,13 +25044,13 @@
         <v>82</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>82</v>
@@ -25070,31 +25068,31 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>743</v>
+        <v>796</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>82</v>
@@ -25102,10 +25100,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25113,7 +25111,7 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G190" t="s" s="2">
         <v>92</v>
@@ -25128,19 +25126,19 @@
         <v>93</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>232</v>
+        <v>802</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>798</v>
+        <v>551</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>411</v>
+        <v>540</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -25165,34 +25163,34 @@
         <v>82</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="Z190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF190" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="AA190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>796</v>
-      </c>
       <c r="AG190" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>92</v>
@@ -25207,24 +25205,24 @@
         <v>82</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>416</v>
+        <v>545</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25244,22 +25242,22 @@
         <v>82</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>804</v>
+        <v>232</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>539</v>
+        <v>808</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>528</v>
+        <v>650</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -25284,13 +25282,13 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -25308,7 +25306,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25317,7 +25315,7 @@
         <v>92</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>104</v>
@@ -25326,35 +25324,35 @@
         <v>82</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>807</v>
+        <v>82</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>533</v>
+        <v>229</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>82</v>
@@ -25369,16 +25367,16 @@
         <v>232</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>811</v>
+        <v>658</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25406,10 +25404,10 @@
         <v>149</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25427,16 +25425,16 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>104</v>
@@ -25445,28 +25443,28 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>229</v>
+        <v>663</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>82</v>
+        <v>664</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -25485,19 +25483,19 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>232</v>
+        <v>83</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>658</v>
+        <v>732</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>659</v>
+        <v>733</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
@@ -25522,13 +25520,13 @@
         <v>82</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25546,7 +25544,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25564,139 +25562,20 @@
         <v>82</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>663</v>
+        <v>735</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="194" hidden="true">
-      <c r="A194" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO194" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO194">
+  <autoFilter ref="A1:AO193">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25706,7 +25585,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI193">
+  <conditionalFormatting sqref="A2:AI192">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:49:26+00:00</t>
+    <t>2026-08-28T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:02+00:00</t>
+    <t>2026-08-28T10:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:19:24+00:00</t>
+    <t>2026-09-01T07:28:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7213" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7213" uniqueCount="818">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:28:55+00:00</t>
+    <t>2026-09-01T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2075,10 +2075,10 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollständige ValueSet Observation Interpretation Codes; das Modul schränkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible ist, dürfen darüber hinaus weitere Codes verwendet werden; praktisch relevant sind die abnormal-Codes HH, LL und AA, etwa für Werte jenseits der Telefongrenze.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -2553,6 +2553,12 @@
   </si>
   <si>
     <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2909,7 +2915,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="140.3671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="86.3984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -25404,10 +25410,10 @@
         <v>149</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>660</v>
+        <v>813</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>661</v>
+        <v>814</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25457,10 +25463,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25486,10 +25492,10 @@
         <v>83</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>732</v>
@@ -25544,7 +25550,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:17:52+00:00</t>
+    <t>2026-09-01T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:26:20+00:00</t>
+    <t>2026-09-01T11:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:37:07+00:00</t>
+    <t>2026-09-01T11:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:44:40+00:00</t>
+    <t>2026-09-01T12:05:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:05:15+00:00</t>
+    <t>2026-09-01T12:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:12:27+00:00</t>
+    <t>2026-09-01T12:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:31:59+00:00</t>
+    <t>2026-09-01T12:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:37:11+00:00</t>
+    <t>2026-09-01T12:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:41:57+00:00</t>
+    <t>2026-09-01T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:58:26+00:00</t>
+    <t>2026-09-01T13:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:38:20+00:00</t>
+    <t>2026-09-01T13:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:44:38+00:00</t>
+    <t>2026-09-01T14:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:35:41+00:00</t>
+    <t>2026-09-01T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1759,7 +1759,7 @@
     <t>pqTranslation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {extension-quantity-translation}
+    <t xml:space="preserve">Extension {extension-quantity-translation|5.2.0}
 </t>
   </si>
   <si>
@@ -1819,7 +1819,7 @@
     <t>quantityPrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {quantity-precision}
+    <t xml:space="preserve">Extension {quantity-precision|5.2.0}
 </t>
   </si>
   <si>
@@ -17333,7 +17333,7 @@
         <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>120</v>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:11:46+00:00</t>
+    <t>2026-09-01T15:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:27:37+00:00</t>
+    <t>2026-09-01T15:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:32:49+00:00</t>
+    <t>2026-09-01T15:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:38:53+00:00</t>
+    <t>2026-09-01T16:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:17:13+00:00</t>
+    <t>2026-09-01T16:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:23:29+00:00</t>
+    <t>2026-09-02T06:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:57:39+00:00</t>
+    <t>2026-09-02T07:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:24:40+00:00</t>
+    <t>2026-09-02T08:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:07:59+00:00</t>
+    <t>2026-09-02T09:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:10:52+00:00</t>
+    <t>2026-09-02T09:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:21:54+00:00</t>
+    <t>2026-09-02T10:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:32:32+00:00</t>
+    <t>2026-09-02T10:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:47:13+00:00</t>
+    <t>2026-09-02T11:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:41:16+00:00</t>
+    <t>2026-09-02T11:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
